--- a/final_outputs/figure_b_distribution.xlsx
+++ b/final_outputs/figure_b_distribution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\international-tax-competitiveness-index\final_outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB57769-FB60-4E52-A44E-DF8C7B4CA3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF4B253-4898-4D76-BEFA-AD798742A7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{7939B179-B2E8-475D-84F7-774A10E48CF3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{7939B179-B2E8-475D-84F7-774A10E48CF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -152,10 +152,10 @@
     <t>France</t>
   </si>
   <si>
-    <t>country</t>
-  </si>
-  <si>
-    <t>score</t>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Final Score</t>
   </si>
 </sst>
 </file>
@@ -288,7 +288,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>score</c:v>
+                  <c:v>Final Score</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -330,94 +330,94 @@
                   <c:v>Australia</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>Czech Republic</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>Israel</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
+                  <c:v>Turkey</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>Hungary</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>Czech Republic</c:v>
-                </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>Sweden</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>Turkey</c:v>
-                </c:pt>
                 <c:pt idx="12">
+                  <c:v>Slovak Republic</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Costa Rica</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>Canada</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Slovak Republic</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>United States</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>Netherlands</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>Costa Rica</c:v>
+                  <c:v>United States</c:v>
                 </c:pt>
                 <c:pt idx="17">
+                  <c:v>Austria</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Norway</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>Chile</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>Mexico</c:v>
                 </c:pt>
-                <c:pt idx="18">
-                  <c:v>Austria</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Germany</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>Norway</c:v>
-                </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
+                  <c:v>Finland</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>Greece</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>Korea</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>Japan</c:v>
                 </c:pt>
-                <c:pt idx="22">
-                  <c:v>Greece</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>Finland</c:v>
-                </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="26">
                   <c:v>Slovenia</c:v>
                 </c:pt>
-                <c:pt idx="25">
-                  <c:v>Korea</c:v>
-                </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
+                  <c:v>Belgium</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>Poland</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>Iceland</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>Denmark</c:v>
                 </c:pt>
-                <c:pt idx="27">
-                  <c:v>Chile</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>Iceland</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>Belgium</c:v>
-                </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
                   <c:v>Ireland</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>United Kingdom</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="33">
                   <c:v>Portugal</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="34">
                   <c:v>Spain</c:v>
                 </c:pt>
-                <c:pt idx="34">
-                  <c:v>Poland</c:v>
-                </c:pt>
                 <c:pt idx="35">
+                  <c:v>Italy</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>Colombia</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>Italy</c:v>
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>France</c:v>
@@ -435,115 +435,115 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>92.84393523</c:v>
+                  <c:v>92.478921479331802</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>87.813627539999999</c:v>
+                  <c:v>90.026071776069301</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>86.022021199999998</c:v>
+                  <c:v>86.775669371845098</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>81.833497039999997</c:v>
+                  <c:v>82.553329099630204</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>80.95664979</c:v>
+                  <c:v>81.903410132011203</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>79.684170809999998</c:v>
+                  <c:v>80.0527199939892</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>78.858911370000001</c:v>
+                  <c:v>79.814996678054001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>78.732951240000006</c:v>
+                  <c:v>77.645546207861599</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>77.363308669999995</c:v>
+                  <c:v>76.419714036643001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>76.100552239999999</c:v>
+                  <c:v>76.333261640680902</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>75.857236499999999</c:v>
+                  <c:v>75.597444025541293</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>73.898954599999996</c:v>
+                  <c:v>74.7101959668733</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>73.307153749999998</c:v>
+                  <c:v>74.151963588780305</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>72.477950820000004</c:v>
+                  <c:v>73.687043974057602</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>71.428410670000005</c:v>
+                  <c:v>71.601313881173894</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>71.421304480000003</c:v>
+                  <c:v>71.571353403292804</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>70.125859520000006</c:v>
+                  <c:v>70.906301436919406</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>69.645655579999996</c:v>
+                  <c:v>69.198361009133905</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>68.886740639999999</c:v>
+                  <c:v>68.048926428257104</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>68.827396890000003</c:v>
+                  <c:v>67.221508094223296</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>67.790869369999996</c:v>
+                  <c:v>67.198007694867798</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>67.022451290000006</c:v>
+                  <c:v>66.215730326106097</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>66.792504789999995</c:v>
+                  <c:v>65.851998199487198</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>66.78833496</c:v>
+                  <c:v>64.992270623016296</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>66.346349840000002</c:v>
+                  <c:v>64.688298075990204</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>64.290688149999994</c:v>
+                  <c:v>64.5499167722474</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>63.784252819999999</c:v>
+                  <c:v>63.500136288337202</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>63.676040290000003</c:v>
+                  <c:v>63.458745291191299</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>63.24646181</c:v>
+                  <c:v>63.163904189766001</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>61.314929210000003</c:v>
+                  <c:v>62.945740192263898</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>59.062778989999998</c:v>
+                  <c:v>62.177908096534601</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>58.228953279999999</c:v>
+                  <c:v>60.842437667295698</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>57.910287949999997</c:v>
+                  <c:v>59.585475440643997</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>54.711228290000001</c:v>
+                  <c:v>57.524840338337</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>51.148387929999998</c:v>
+                  <c:v>50.763076487372302</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>50.295762830000001</c:v>
+                  <c:v>49.228990399474398</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>45.771647770000001</c:v>
+                  <c:v>45.720921215802797</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1308,8 +1308,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0C8726FB-6A84-4EDC-BF2F-88BFE736C5CB}" name="Table3" displayName="Table3" ref="A1:B39" totalsRowShown="0">
   <autoFilter ref="A1:B39" xr:uid="{0C8726FB-6A84-4EDC-BF2F-88BFE736C5CB}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E30BF9EF-CB32-4AF6-95C2-7B9B9172AE7E}" name="country" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{618FC723-9633-4957-99BA-47045360625D}" name="score" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{E30BF9EF-CB32-4AF6-95C2-7B9B9172AE7E}" name="Country" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{618FC723-9633-4957-99BA-47045360625D}" name="Final Score" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1636,7 +1636,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2">
-        <v>92.84393523</v>
+        <v>92.478921479331802</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
@@ -1644,7 +1644,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1">
-        <v>87.813627539999999</v>
+        <v>90.026071776069301</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
@@ -1652,7 +1652,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>86.022021199999998</v>
+        <v>86.775669371845098</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
@@ -1660,7 +1660,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="1">
-        <v>81.833497039999997</v>
+        <v>82.553329099630204</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
@@ -1668,7 +1668,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>80.95664979</v>
+        <v>81.903410132011203</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
@@ -1676,71 +1676,71 @@
         <v>12</v>
       </c>
       <c r="B8" s="1">
-        <v>79.684170809999998</v>
+        <v>80.0527199939892</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>78.858911370000001</v>
+        <v>79.814996678054001</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1">
-        <v>78.732951240000006</v>
+        <v>77.645546207861599</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>77.363308669999995</v>
+        <v>76.419714036643001</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B12" s="1">
-        <v>76.100552239999999</v>
+        <v>76.333261640680902</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>75.857236499999999</v>
+        <v>75.597444025541293</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1">
-        <v>73.898954599999996</v>
+        <v>74.7101959668733</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B15" s="2">
-        <v>73.307153749999998</v>
+        <v>74.151963588780305</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1">
-        <v>72.477950820000004</v>
+        <v>73.687043974057602</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
@@ -1748,175 +1748,175 @@
         <v>13</v>
       </c>
       <c r="B17" s="2">
-        <v>71.428410670000005</v>
+        <v>71.601313881173894</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="1">
-        <v>71.421304480000003</v>
+        <v>71.571353403292804</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2">
-        <v>70.125859520000006</v>
+        <v>70.906301436919406</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B20" s="1">
-        <v>69.645655579999996</v>
+        <v>69.198361009133905</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B21" s="2">
-        <v>68.886740639999999</v>
+        <v>68.048926428257104</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1">
-        <v>68.827396890000003</v>
+        <v>67.221508094223296</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2">
-        <v>67.790869369999996</v>
+        <v>67.198007694867798</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B24" s="1">
-        <v>67.022451290000006</v>
+        <v>66.215730326106097</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>66.792504789999995</v>
+        <v>65.851998199487198</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B26" s="1">
-        <v>66.78833496</v>
+        <v>64.992270623016296</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B27" s="2">
-        <v>66.346349840000002</v>
+        <v>64.688298075990204</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B28" s="1">
-        <v>64.290688149999994</v>
+        <v>64.5499167722474</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B29" s="2">
-        <v>63.784252819999999</v>
+        <v>63.500136288337202</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" s="1">
-        <v>63.676040290000003</v>
+        <v>63.458745291191299</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B31" s="2">
-        <v>63.24646181</v>
+        <v>63.163904189766001</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B32" s="1">
-        <v>61.314929210000003</v>
+        <v>62.945740192263898</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B33" s="2">
-        <v>59.062778989999998</v>
+        <v>62.177908096534601</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B34" s="1">
-        <v>58.228953279999999</v>
+        <v>60.842437667295698</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B35" s="2">
-        <v>57.910287949999997</v>
+        <v>59.585475440643997</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B36" s="1">
-        <v>54.711228290000001</v>
+        <v>57.524840338337</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B37" s="2">
-        <v>51.148387929999998</v>
+        <v>50.763076487372302</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B38" s="1">
-        <v>50.295762830000001</v>
+        <v>49.228990399474398</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
@@ -1924,7 +1924,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>45.771647770000001</v>
+        <v>45.720921215802797</v>
       </c>
     </row>
   </sheetData>
